--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N107_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N107_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>113.1520014719507</v>
+        <v>18.38720023919199</v>
       </c>
       <c r="D2" t="n">
-        <v>113.0164056681502</v>
+        <v>18.3651659210744</v>
       </c>
       <c r="E2" t="n">
-        <v>50.10977228946393</v>
+        <v>8.142837997037891</v>
       </c>
       <c r="F2" t="n">
-        <v>50.29540568061332</v>
+        <v>8.173003423099665</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.93245689302281</v>
+        <v>2.101524245116206</v>
       </c>
       <c r="D3" t="n">
-        <v>12.42559430692353</v>
+        <v>2.019159074875073</v>
       </c>
       <c r="E3" t="n">
-        <v>50.10977228946393</v>
+        <v>8.142837997037891</v>
       </c>
       <c r="F3" t="n">
-        <v>50.29540568061332</v>
+        <v>8.173003423099665</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
